--- a/Documentation/faraway_data_sanctuaries.xlsx
+++ b/Documentation/faraway_data_sanctuaries.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\GitHub\Faraway-Project\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\FLo\GitHub\Faraway-Project - Copie\Faraway\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43EB356A-1BE6-4359-A1EC-E43AEBDA4CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8530BBD-2F88-442C-87D8-221B4FD65ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{76B5293A-A2AF-4A0E-9BCB-5328EF920223}"/>
+    <workbookView xWindow="75" yWindow="2490" windowWidth="28800" windowHeight="15435" xr2:uid="{76B5293A-A2AF-4A0E-9BCB-5328EF920223}"/>
   </bookViews>
   <sheets>
     <sheet name="sanctuaries" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -69,40 +69,40 @@
     <t>rb</t>
   </si>
   <si>
-    <t>antilope</t>
-  </si>
-  <si>
-    <t>mana</t>
-  </si>
-  <si>
-    <t>pineapple</t>
-  </si>
-  <si>
     <t>map</t>
   </si>
   <si>
     <t>gbyr</t>
   </si>
   <si>
-    <t>mana,map</t>
-  </si>
-  <si>
-    <t>antilope,map</t>
-  </si>
-  <si>
-    <t>pineapple,map</t>
-  </si>
-  <si>
     <t>night</t>
   </si>
   <si>
-    <t>mana,night</t>
-  </si>
-  <si>
-    <t>antilope,night</t>
-  </si>
-  <si>
-    <t>pineapple,night</t>
+    <t>chimera</t>
+  </si>
+  <si>
+    <t>chimera,map</t>
+  </si>
+  <si>
+    <t>chimera,night</t>
+  </si>
+  <si>
+    <t>stone</t>
+  </si>
+  <si>
+    <t>stone,map</t>
+  </si>
+  <si>
+    <t>stone,night</t>
+  </si>
+  <si>
+    <t>thistle</t>
+  </si>
+  <si>
+    <t>thistle,map</t>
+  </si>
+  <si>
+    <t>thistle,night</t>
   </si>
 </sst>
 </file>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC520287-E6EB-4D7E-8B9D-0537053412EF}">
   <dimension ref="A1:E47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -471,7 +471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -499,7 +499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -513,7 +513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -527,7 +527,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -549,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -582,7 +582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -593,133 +593,133 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -728,12 +728,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -742,7 +742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -750,105 +750,105 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -857,132 +857,132 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" t="s">
         <v>14</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
       <c r="D37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -990,7 +990,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
